--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -493,10 +493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>Validateur de profil ICC</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>Validateur de profil ICC · propulsé par IccProfLib</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -643,9 +643,321 @@
         <v>Erreur :</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Convertir en XML</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Convertir en JSON</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Convertir en ICC</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Conversion en XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Conversion en JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Conversion en ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Charger un profil ICC</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ID du profil</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Aucune balise trouvée.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Nom de balise</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Décalage</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Taille</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Rembourrage</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Octets modifiés depuis le chargement</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Type</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Tableau de {type}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(Aucun contenu)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>octets</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Chargement de la description complète…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Impossible de charger la description complète :</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -869,95 +869,175 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>indentation</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>trier les clés</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -821,223 +821,239 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>Valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>Avertissement</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>Erreur</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>Inconnu</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>Détail de validation</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>Déclenché par</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>Champ</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>Valeur actuelle</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>Requis : 0</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>Attendu : {value}</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>Non valide</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>Fermer</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>trier les clés</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -845,215 +845,263 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>Valide</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>Avertissement</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>Erreur</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>Inconnu</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>Détail de validation</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>Déclenché par</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>Champ</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>Valeur actuelle</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>Requis : 0</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>Attendu : {value}</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>Non valide</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>Fermer</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>indentation</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>trier les clés</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,503 +605,591 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>Sortie brute</v>
+        <v>Profile Assessment WG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>Erreur :</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>Convertir en XML</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>Convertir en JSON</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>Convertir en ICC</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>Conversion en XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>Conversion en JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>Conversion en ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>Charger un profil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>ID du profil</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>Nom de balise</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>Décalage</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>Taille</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>Rembourrage</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>Type</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>Tableau de {type}</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>octets</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>Le profil est valide</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>État de validation inconnu</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>Valide</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>Avertissement</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>Erreur</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>Inconnu</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>Détail de validation</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>Déclenché par</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>Champ</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>Valeur actuelle</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>Requis : 0</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>Attendu : {value}</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>Non valide</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>Fermer</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>indentation</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>trier les clés</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -637,23 +637,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -661,7 +661,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -669,7 +669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -677,7 +677,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -685,7 +685,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -693,7 +693,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -701,7 +701,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -709,7 +709,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -717,479 +717,495 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>Erreur :</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>Convertir en XML</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>Convertir en JSON</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>ID du profil</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>Nom de balise</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>Décalage</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>Taille</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>Rembourrage</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>Type</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>Tableau de {type}</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>octets</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>Le profil est valide</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>État de validation inconnu</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>Valide</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>Avertissement</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>Erreur</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>Inconnu</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>Détail de validation</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>Déclenché par</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>Champ</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>Valeur actuelle</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>Requis : 0</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>Attendu : {value}</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>Non valide</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>Fermer</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>trier les clés</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -512,12 +512,12 @@
         <v>specification using the</v>
       </c>
       <c r="B14" t="str">
-        <v>à l’aide de l’implémentation de référence</v>
+        <v>à l’aide de l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
         <v>.</v>
@@ -525,687 +525,919 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>Validation…</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>ou</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>Choisir un fichier</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>En-tête</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>Balises</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>Validation</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>Sortie brute</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>URL de profil non valide :</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Tables</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>Erreur :</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>Convertir en XML</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>Convertir en JSON</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>Convertir en ICC</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>Conversion en XML…</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>ID du profil</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>Nom de balise</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>Décalage</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>Taille</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>Rembourrage</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>Type</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>Tableau de {type}</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(Aucun contenu)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>octets</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>Chargement de la description complète…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>Aucune sortie de validation</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>Le profil est valide</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>État de validation inconnu</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>Valide</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>Avertissement</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>Erreur</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>Inconnu</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>Détail de validation</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Déclenché par</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>Champ</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>Valeur actuelle</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>Requis : 0</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>Attendu : {value}</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>Non valide</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>Fermer</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>indentation</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>trier les clés</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -861,583 +861,575 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>Erreur :</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>Convertir en XML</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>Convertir en ICC</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>Conversion en XML…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>ID du profil</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>Nom de balise</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>Décalage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>Taille</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>Rembourrage</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>Type</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>Tableau de {type}</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(Aucun contenu)</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>octets</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>Le profil est valide</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>Erreur de validation critique</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>État de validation inconnu</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>Valide</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>Avertissement</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>Erreur</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>Inconnu</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>Réussi</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>Échec</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>Détail de validation</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>Déclenché par</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>Champ</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>Valeur actuelle</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>Requis : 0</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>Attendu : {value}</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>Non valide</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>Fermer</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>indentation</v>
+        <v>trier les clés</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>trier les clés</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -477,959 +477,983 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>Aide</v>
+        <v>Format des nombres</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>Contact</v>
+        <v>Hexadécimal</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Décimal</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
+        <v>Aide</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>à l’aide de l’implémentation de démonstration</v>
+        <v>Contact</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>à l’aide de l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>Validation…</v>
+        <v>.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>ou</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>Choisir un fichier</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>En-tête</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>Balises</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>Validation</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Tracé</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>Sortie brute</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>Courbes</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>Courbes d’entrée</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>Courbes de sortie</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>Image CLUT</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>Image de gamut</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>Chromaticité</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>Nuage de points</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>Table de la courbe</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>Tables</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>Données</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>Évaluer</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>Chargement…</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>Entrée</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>Sortie</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>Virgule flottante</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>Point de grille</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>Normalisé</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>Lisible</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>Appareil → PCS</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → Appareil</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>Chargement…</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>Sécurité</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>Conformité</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>Qualité</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>RAPPORT</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>ÉCHEC</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>contrôles</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>Erreur :</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>Convertir en XML</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>Convertir en JSON</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>Convertir en ICC</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>ID du profil</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>Nom de balise</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>Décalage</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>Taille</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>Rembourrage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>Type</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>Tableau de {type}</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>octets</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>Le profil est valide</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>État de validation inconnu</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>Valide</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>Avertissement</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>Erreur</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>Inconnu</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>Réussi</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>Échec</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>Détail de validation</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>Déclenché par</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>Champ</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>Valeur actuelle</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>Requis : 0</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>Attendu : {value}</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>Non valide</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>Fermer</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>indentation</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>trier les clés</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -885,575 +885,583 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>Sécurité</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>Conformité</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>Qualité</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>RAPPORT</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>Erreur :</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B132"/>
+  <dimension ref="A1:B181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -645,823 +645,1215 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>Tracé</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>Sortie brute</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>Courbes</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>Courbes de sortie</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>Image CLUT</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>Image de gamut</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>Chromaticité</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>Nuage de points</v>
+        <v>Les canaux à nombreuses inversions n’affichent que les {shown} plus grandes par ΔL*.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Afficher plus ({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>Table de la courbe</v>
+        <v>Tous</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>Tables</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>Données</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>Évaluer</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>Chargement…</v>
+        <v>Inversion de tonalité L*</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>Entrée</v>
+        <v>Ajouter de l’encre ne devrait jamais éclaircir une couleur. Chaque canal est balayé, les autres maintenus fixes ; toute étape où L* augmente est signalée. Algorithme dû à l’origine à Harold Boll.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>Sortie</v>
+        <v>Aucune CLUT périphérique→PCS dans ce profil : l’analyse d’inversion L* ne s’applique pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>Virgule flottante</v>
+        <v>Table LUT</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>Point de grille</v>
+        <v>Seuil ΔL* (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>Normalisé</v>
+        <v>{n} inversions au-dessus de ε = {eps}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>Lisible</v>
+        <v>Aucune inversion L* au-dessus de ε = {eps}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>Appareil → PCS</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → Appareil</v>
+        <v>Encre (bas → haut)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>Chargement…</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>URL de profil non valide :</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>Sécurité</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>Conformité</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>Qualité</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>RAPPORT</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>ÉCHEC</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>contrôles</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>Erreur :</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>Convertir en XML</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>Convertir en JSON</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>Convertir en ICC</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>Conversion en XML…</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>Charger un profil ICC</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>ID du profil</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>Nom de balise</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>Décalage</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>Taille</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>Rembourrage</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>Type</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>Tableau de {type}</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>octets</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>Le profil est valide</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>État de validation inconnu</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>Valide</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>Avertissement</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>Erreur</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>Inconnu</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>Réussi</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>Échec</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>Voir dans le contexte</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>Détail de validation</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>Déclenché par</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>Champ</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>Valeur actuelle</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>Requis : 0</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>Attendu : {value}</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>Non valide</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>Fermer</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>indentation</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>trier les clés</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Aucune balise trouvée.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Nom de balise</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Décalage</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Taille</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Rembourrage</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Octets modifiés depuis le chargement</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Type</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Tableau de {type}</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(Aucun contenu)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>octets</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Chargement de la description complète…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Impossible de charger la description complète :</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Le profil est valide</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Le profil comporte des avertissements</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Le profil est non conforme</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Erreur de validation critique</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -517,1343 +517,1415 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Guide de l’utilisateur</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
+        <v>Rechercher dans le guide</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>à l’aide de l’implémentation de démonstration</v>
+        <v>Rechercher dans le guide de l’utilisateur</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>.</v>
+        <v>Résultat précédent</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Résultat suivant</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Fermer le guide</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>Validation…</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Impossible de charger le guide de l’utilisateur.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>Aucun</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>ou</v>
+        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>Choisir un fichier</v>
+        <v>à l’aide de l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>En-tête</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>Balises</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>Validation</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>Analyse</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>Intention de rendu</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% encre</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>Perceptif</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>Saturation</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>Les canaux à nombreuses inversions n’affichent que les {shown} plus grandes par ΔL*.</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>Afficher plus ({n})</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>Tous</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>Analyse en cours…</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>Analyse</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>Inversion de tonalité L*</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>Ajouter de l’encre ne devrait jamais éclaircir une couleur. Chaque canal est balayé, les autres maintenus fixes ; toute étape où L* augmente est signalée. Algorithme dû à l’origine à Harold Boll.</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>Aucune CLUT périphérique→PCS dans ce profil : l’analyse d’inversion L* ne s’applique pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>Table LUT</v>
+        <v>Les canaux à nombreuses inversions n’affichent que les {shown} plus grandes par ΔL*.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>Seuil ΔL* (ε)</v>
+        <v>Afficher plus ({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>{n} inversions au-dessus de ε = {eps}</v>
+        <v>Tous</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>Aucune inversion L* au-dessus de ε = {eps}</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>Canal</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>Encre (bas → haut)</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>Tracé</v>
+        <v>Inversion de tonalité L*</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>Sortie brute</v>
+        <v>Ajouter de l’encre ne devrait jamais éclaircir une couleur. Chaque canal est balayé, les autres maintenus fixes ; toute étape où L* augmente est signalée. Algorithme dû à l’origine à Harold Boll.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>Aucune CLUT périphérique→PCS dans ce profil : l’analyse d’inversion L* ne s’applique pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>Table LUT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>Courbes</v>
+        <v>Seuil ΔL* (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>Courbes d’entrée</v>
+        <v>{n} inversions au-dessus de ε = {eps}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>Courbes de sortie</v>
+        <v>Aucune inversion L* au-dessus de ε = {eps}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>Image CLUT</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>Image de gamut</v>
+        <v>Encre (bas → haut)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>Chromaticité</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>Nuage de points</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>Table de la courbe</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tables</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Données</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>Évaluer</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>Chargement…</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>Entrée</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>Sortie</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Virgule flottante</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>Point de grille</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>Normalisé</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>Lisible</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>Appareil → PCS</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → Appareil</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>Chargement…</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>Sécurité</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>Conformité</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>Qualité</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>RAPPORT</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>ÉCHEC</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>contrôles</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>S’abonner</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>Fermer</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>Adresse e-mail</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>vous@exemple.com</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(facultatif)</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>Annuler</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>S’abonner</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>Fermer</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>Erreur :</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>Convertir en XML</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>Convertir en JSON</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>Convertir en ICC</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>Conversion en XML…</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>ID du profil</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>Nom de balise</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>Décalage</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>Taille</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>Rembourrage</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>Type</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>Tableau de {type}</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>octets</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>Le profil est valide</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>Le profil est non conforme</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>Erreur de validation critique</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>État de validation inconnu</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>Valide</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>Avertissement</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>Erreur</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>Inconnu</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>Réussi</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>Échec</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>Voir dans le contexte</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>Détail de validation</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>Déclenché par</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>Champ</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>Valeur actuelle</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>Requis : 0</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>Attendu : {value}</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>Non valide</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>Fermer</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>indentation</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>trier les clés</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -797,330 +797,330 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>Les canaux à nombreuses inversions n’affichent que les {shown} plus grandes par ΔL*.</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>Afficher plus ({n})</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>Tous</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>Analyse en cours…</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>Analyse</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>Inversion de tonalité L*</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>Ajouter de l’encre ne devrait jamais éclaircir une couleur. Chaque canal est balayé, les autres maintenus fixes ; toute étape où L* augmente est signalée. Algorithme dû à l’origine à Harold Boll.</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>Aucune CLUT périphérique→PCS dans ce profil : l’analyse d’inversion L* ne s’applique pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>Table LUT</v>
+        <v>max</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>Seuil ΔL* (ε)</v>
+        <v>Les canaux à nombreuses inversions n’affichent que les {shown} plus grandes par ΔL*.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>{n} inversions au-dessus de ε = {eps}</v>
+        <v>Afficher plus ({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>Aucune inversion L* au-dessus de ε = {eps}</v>
+        <v>Tous</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>Canal</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>Encre (bas → haut)</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>Tracé</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>Sortie brute</v>
+        <v>Inversion de tonalité L*</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>Ajouter de l’encre ne devrait jamais éclaircir une couleur. Chaque canal est balayé, les autres maintenus fixes ; toute étape où L* augmente est signalée. Algorithme dû à l’origine à Harold Boll.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>Aucune CLUT périphérique→PCS dans ce profil : l’analyse d’inversion L* ne s’applique pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>Courbes</v>
+        <v>Table LUT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Seuil ΔL* (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>Courbes de sortie</v>
+        <v>{n} inversions au-dessus de ε = {eps}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>Image CLUT</v>
+        <v>Aucune inversion L* au-dessus de ε = {eps}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>Image de gamut</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>Chromaticité</v>
+        <v>Encre (bas → haut)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Nuage de points</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>Table de la courbe</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>Données</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>Évaluer</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>Chargement…</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>Entrée</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>Sortie</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>Virgule flottante</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>Point de grille</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>Normalisé</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>Lisible</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>Appareil → PCS</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → Appareil</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="91">
@@ -1133,799 +1133,879 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>Sécurité</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>Conformité</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>Qualité</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>RAPPORT</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>ÉCHEC</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>contrôles</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>S’abonner</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>Fermer</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>Adresse e-mail</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>vous@exemple.com</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(facultatif)</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>Annuler</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>S’abonner</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>Fermer</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>Avis de confidentialité</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>Erreur :</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>Convertir en XML</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>Convertir en JSON</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>Convertir en ICC</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>Conversion en XML…</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>ID du profil</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>Nom de balise</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>Décalage</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>Taille</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>Rembourrage</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>Type</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>Tableau de {type}</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(Aucun contenu)</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>octets</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>Le profil est valide</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>Erreur de validation critique</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>État de validation inconnu</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>Valide</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>Avertissement</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>Erreur</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>Inconnu</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>Réussi</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>Échec</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>Détail de validation</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>Déclenché par</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>Champ</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>Valeur actuelle</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>Requis : 0</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>Attendu : {value}</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>Non valide</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>Fermer</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>indentation</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>trier les clés</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B200"/>
+  <dimension ref="A1:B188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -877,474 +877,474 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>Les canaux à nombreuses inversions n’affichent que les {shown} plus grandes par ΔL*.</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>Afficher plus ({n})</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>Tous</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>Analyse en cours…</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>Analyse</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>Inversion de tonalité L*</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>Ajouter de l’encre ne devrait jamais éclaircir une couleur. Chaque canal est balayé, les autres maintenus fixes ; toute étape où L* augmente est signalée. Algorithme dû à l’origine à Harold Boll.</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Aucune CLUT périphérique→PCS dans ce profil : l’analyse d’inversion L* ne s’applique pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Table LUT</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>Seuil ΔL* (ε)</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>{n} inversions au-dessus de ε = {eps}</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>Aucune inversion L* au-dessus de ε = {eps}</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>Canal</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>Encre (bas → haut)</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>Tracé</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>Sortie brute</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Courbes</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>Courbes de sortie</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>Image CLUT</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>Image de gamut</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>Chromaticité</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>Nuage de points</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>Table de la courbe</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>Tables</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>Données</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>Évaluer</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>Chargement…</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>Entrée</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>Sortie</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>Virgule flottante</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>Point de grille</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>Normalisé</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>Lisible</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>Appareil → PCS</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → Appareil</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>Chargement…</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Sécurité</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>Conformité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>Qualité</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>RAPPORT</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>ÉCHEC</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>contrôles</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>Outil de profil ICC</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="119">
@@ -1357,18 +1357,18 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="122">
@@ -1381,631 +1381,535 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>Adresse e-mail</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>vous@exemple.com</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(facultatif)</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>Annuler</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>S’abonner</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>Fermer</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>Erreur :</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>Convertir en XML</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>Convertir en JSON</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>Convertir en ICC</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>Conversion en XML…</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>Charger un profil ICC</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>ID du profil</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>Nom de balise</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>Décalage</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>Taille</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>Rembourrage</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>Type</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>Tableau de {type}</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>octets</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>Le profil est valide</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>État de validation inconnu</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>Valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>Avertissement</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>Erreur</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>Inconnu</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>Réussi</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Échec</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Détail de validation</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>Déclenché par</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>Champ</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>Valeur actuelle</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Requis : 0</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>Attendu : {value}</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>Non valide</v>
+        <v>trier les clés</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Fermer</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>Chargement de l’éditeur XML…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● modifications XML non enregistrées</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● modifications JSON non enregistrées</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>indentation</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>trier les clés</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -853,1063 +853,1071 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>moyenne</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>Analyse en cours…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>Analyse</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>Tracé</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>Sortie brute</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>Courbes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Courbes de sortie</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Image CLUT</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>Image de gamut</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>Chromaticité</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>Nuage de points</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>Table de la courbe</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>Tables</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>Données</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>Évaluer</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>Chargement…</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>Entrée</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>Sortie</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>Virgule flottante</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>Point de grille</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>Normalisé</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>Lisible</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>Appareil → PCS</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → Appareil</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>Chargement…</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>Sécurité</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>Conformité</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>Qualité</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>RAPPORT</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,1511 +413,1887 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>Paramètres</v>
+        <v>Aller-retour (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>Affichage</v>
+        <v>Aller-retour sur le cube périphérique du profil, identique à l’outil de référence iccRoundTrip. L’aller-retour 1 correspond à l’erreur périphérique→PCS→périphérique (ΔE*ab) ; l’aller-retour 2 mesure la stabilité de l’aller-retour PCS. L’histogramme PRMG indique l’interopérabilité par rapport au Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>Arrière-plan</v>
+        <v>Utiliser les balises MPE (couleur)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>Langue</v>
+        <v>Ce profil ne peut pas faire d’aller-retour : il lui manque les transformations périphérique↔PCS requises (par ex. un profil unidirectionnel ou abstrait).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>Système</v>
+        <v>Aller-retour ignoré : l’espace colorimétrique du périphérique est trop large à évaluer (trop d’échantillons).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>Clair</v>
+        <v>Métrique</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>Sombre</v>
+        <v>Aller-retour 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>Par défaut du système</v>
+        <v>Aller-retour 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>Format des nombres</v>
+        <v>périphérique → PCS → périphérique</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>Hexadécimal</v>
+        <v>stabilité de l’aller-retour PCS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>Décimal</v>
+        <v>ΔE min</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Aide</v>
+        <v>ΔE moyen</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Contact</v>
+        <v>ΔE max</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>Guide de l’utilisateur</v>
+        <v>Pire L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>Rechercher dans le guide</v>
+        <v>Gamut spécifié</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Rechercher dans le guide de l’utilisateur</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>Résultat précédent</v>
+        <v>Non spécifié</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>Résultat suivant</v>
+        <v>Non évalué</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>Fermer le guide</v>
+        <v>Interopérabilité PRMG</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>Chargement…</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>Impossible de charger le guide de l’utilisateur.</v>
+        <v>Nombre</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>Aucun</v>
+        <v>Part</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
+        <v>PRMG non évalué</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>à l’aide de l’implémentation de démonstration</v>
+        <v>Paramètres</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>.</v>
+        <v>Affichage</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Arrière-plan</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Langue</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>Validation…</v>
+        <v>Système</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Clair</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>Sombre</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Par défaut du système</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>ou</v>
+        <v>Format des nombres</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>Choisir un fichier</v>
+        <v>Hexadécimal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Décimal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>En-tête</v>
+        <v>Aide</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>Balises</v>
+        <v>Contact</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>Validation</v>
+        <v>Guide de l’utilisateur</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>Analyse</v>
+        <v>Rechercher dans le guide</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>Rechercher dans le guide de l’utilisateur</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Résultat précédent</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Résultat suivant</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>Fermer le guide</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>Intention de rendu</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% encre</v>
+        <v>Impossible de charger le guide de l’utilisateur.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>Perceptif</v>
+        <v>Aucun</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>Saturation</v>
+        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>à l’aide de l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>Statistiques du profil</v>
+        <v>.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>Intention de rendu</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>ΔE aller-retour</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>moyenne</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>max</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>Analyse en cours…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>Analyse</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>Tracé</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>Sortie brute</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>Courbes</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>Courbes d’entrée</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>Courbes de sortie</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>Image CLUT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>Image de gamut</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>Chromaticité</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>Nuage de points</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>Table de la courbe</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>Tables</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>Données</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>Évaluer</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>Chargement…</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>Entrée</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>Sortie</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>Virgule flottante</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>Point de grille</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>Normalisé</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>Lisible</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>Appareil → PCS</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → Appareil</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>Chargement…</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>Sécurité</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>Conformité</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>Qualité</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>RAPPORT</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>ÉCHEC</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>contrôles</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>Outil de profil ICC</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>max</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>S’abonner</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>Fermer</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>Adresse e-mail</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>vous@exemple.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(facultatif)</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>Annuler</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>S’abonner</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>Fermer</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>Erreur :</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>Convertir en XML</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>Convertir en JSON</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>Convertir en ICC</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>Conversion en XML…</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>Conversion en JSON…</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>ID du profil</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>Nom de balise</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>Décalage</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>Taille</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>Rembourrage</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>Type</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>Tableau de {type}</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(Aucun contenu)</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>octets</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>Le profil est valide</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>État de validation inconnu</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>Valide</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>Avertissement</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>Erreur</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>Inconnu</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>Réussi</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>Échec</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>Détail de validation</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>Déclenché par</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>Champ</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>Valeur actuelle</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>Requis : 0</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>Attendu : {value}</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>Non valide</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>Fermer</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>indentation</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>trier les clés</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Décalage</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Taille</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Rembourrage</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Octets modifiés depuis le chargement</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Type</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Tableau de {type}</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(Aucun contenu)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>octets</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Chargement de la description complète…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Impossible de charger la description complète :</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Le profil est valide</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Le profil comporte des avertissements</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Le profil est non conforme</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Erreur de validation critique</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -605,1695 +605,2365 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>Paramètres</v>
+        <v>Mesures globales du profil pour une intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et une mesure de précision d’aller-retour. Choisissez l’intention de rendu et le type d’aller-retour — le tableau et l’histogramme se mettent à jour en conséquence.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>Affichage</v>
+        <v>Type d’aller-retour</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Arrière-plan</v>
+        <v>Sans effet sur ce type d’aller-retour</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>Langue</v>
+        <v>Ce type d’aller-retour n’est pas disponible pour ce profil.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>Système</v>
+        <v>Distribution du ΔE d’aller-retour</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>Clair</v>
+        <v>Aucun échantillon d’aller-retour n’est tombé dans la région évaluée.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>Sombre</v>
+        <v>Écart-type</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>Par défaut du système</v>
+        <v>Fréquence relative</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Format des nombres</v>
+        <v>Fréquence cumulée</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>Hexadécimal</v>
+        <v>Échelle horizontale</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>Décimal</v>
+        <v>ΔE entier</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>Aide</v>
+        <v>Échelle automatique</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>Contact</v>
+        <v>Classes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>Guide de l’utilisateur</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>Rechercher dans le guide</v>
+        <v>La table de correspondance des couleurs (CLUT) d’une transformation périphérique↔PCS, disposée en mosaïque dans une image. Choisissez la table d’intention de rendu à afficher.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>Rechercher dans le guide de l’utilisateur</v>
+        <v>Ce profil n’a pas de tables périphérique↔PCS basées sur une CLUT à visualiser.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>Résultat précédent</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>Résultat suivant</v>
+        <v>La carte intérieur/extérieur du gamut de la balise gamut : neutre là où une couleur PCS est reproductible, rouge là où elle sort du gamut du périphérique.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>Fermer le guide</v>
+        <v>Ce profil n’a pas de balise gamut à visualiser.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>Chargement…</v>
+        <v>Échelle verticale</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>Impossible de charger le guide de l’utilisateur.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>Aucun</v>
+        <v>Augmentation tonale</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Augmentation tonale (sortie − entrée)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
+        <v>Afficher le vidage complet</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>à l’aide de l’implémentation de démonstration</v>
+        <v>Sortie tronquée pour des raisons de performance.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>.</v>
+        <v>Aperçu dans le gamut (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Reproductibilité (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>Validation…</v>
+        <v>Interopérabilité PRMG</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Aperçu iccviz : une grille de valeurs périphérique est convertie en PCS, de nouveau en périphérique, puis à nouveau en PCS ; le ΔE*ab est mesuré entre les deux passages PCS. Un contrôle rapide de stabilité dans le gamut.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>iccRoundTrip Aller-retour 1 : ΔE*ab entre le PCS de chaque couleur périphérique et son PCS après un aller-retour Lab → périphérique → Lab. Reflète la précision d’inversion et le mappage de gamut.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip Aller-retour 2 : ΔE*ab entre le premier et le second aller-retour — la stabilité d’un aller-retour PCS répété (reproductibilité, indépendamment de l’écrêtage de gamut du premier trajet).</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG : les couleurs PCS à l’intérieur du Perceptual Reference Medium Gamut font un aller-retour unique (Lab → périphérique → Lab) ; la distribution du ΔE*ab indique l’interopérabilité inter-profils.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Paramètres</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Affichage</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Arrière-plan</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Langue</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Système</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Clair</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Sombre</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Par défaut du système</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Format des nombres</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Hexadécimal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Décimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Aide</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Contact</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Guide de l’utilisateur</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Rechercher dans le guide</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Rechercher dans le guide de l’utilisateur</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Résultat précédent</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Résultat suivant</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Fermer le guide</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Impossible de charger le guide de l’utilisateur.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Aucun</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>ou</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>Choisir un fichier</v>
+        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>à l’aide de l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>En-tête</v>
+        <v>.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>Balises</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>Validation</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>Analyse</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Profils</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>Afficher le pool de profils</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>Intention de rendu</v>
+        <v>Réduire</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% encre</v>
+        <v>Charger des profils</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>Perceptif</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Déposez des profils ICC ici</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>Saturation</v>
+        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Nouveau depuis .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>Statistiques du profil</v>
+        <v>Trier par nom</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Nouveau profil depuis .cube</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>Intention de rendu</v>
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Choisir un fichier .cube</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>ΔE aller-retour</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>ou déposez-le ici, ou collez ci-dessous</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>moyenne</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>Créer le DeviceLink</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>max</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>Analyse en cours…</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>Analyse</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Comparer</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>Tracé</v>
+        <v>Lier</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>Sortie brute</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>Courbes</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>Courbes de sortie</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>Image CLUT</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>Image de gamut</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>Chromaticité</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>Nuage de points</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Table de la courbe</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Tables</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Données</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Évaluer</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Chargement…</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Entrée</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Sortie</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Virgule flottante</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Point de grille</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Normalisé</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Lisible</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>Appareil → PCS</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → Appareil</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Chargement…</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Sécurité</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Conformité</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>Qualité</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>RAPPORT</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>ÉCHEC</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>contrôles</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>S’abonner</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Fermer</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>Adresse e-mail</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>vous@exemple.com</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(facultatif)</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>Annuler</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>S’abonner</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>Fermer</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>Erreur :</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>Convertir en XML</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>Convertir en JSON</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>Convertir en ICC</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>Conversion en XML…</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>ID du profil</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>Nom de balise</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>Décalage</v>
+        <v>max</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>Taille</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>Rembourrage</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>Type</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>Tableau de {type}</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(Aucun contenu)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>octets</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>Le profil est valide</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>État de validation inconnu</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>Valide</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>Avertissement</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>Erreur</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>Inconnu</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>Réussi</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>Échec</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>Détail de validation</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>Déclenché par</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>Champ</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>Valeur actuelle</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>Requis : 0</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>Attendu : {value}</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>Non valide</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>Fermer</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>indentation</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>trier les clés</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Outil de profil ICC</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Propulsé par {lib}</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>S’abonner</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Être notifié des nouvelles versions de profiletool</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Être notifié des nouvelles versions</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Adresse e-mail</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>vous@exemple.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Comment utiliserez-vous profiletool ?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(facultatif)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Annuler</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>S’abonner</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Merci — nous reviendrons vers vous.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Avis de confidentialité</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Veuillez saisir une adresse e-mail valide.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Erreur réseau. Veuillez réessayer.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Erreur :</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Convertir en XML</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Convertir en JSON</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Convertir en ICC</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Conversion en XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Conversion en JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Conversion en ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Charger un profil ICC</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>ID du profil</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Aucune balise trouvée.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Nom de balise</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Décalage</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Taille</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Rembourrage</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Octets modifiés depuis le chargement</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Type</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Tableau de {type}</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(Aucun contenu)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>octets</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Chargement de la description complète…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Impossible de charger la description complète :</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Le profil est valide</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Le profil comporte des avertissements</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Le profil est non conforme</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Erreur de validation critique</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>Lier</v>
@@ -1299,1671 +1299,2423 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>Faites glisser des profils du pool vers cet onglet</v>
+        <v>Spectral</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>Retirer</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>Aucun profil sélectionné</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>Rien à comparer pour l’instant</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>Comparaison de gamut</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>Intention de rendu</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>Enveloppe</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>Fil de fer</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacité</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>Couleur</v>
+        <v>Numéros des axes</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>Uni</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>Par valeur</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>Par teinte</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotation</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>Plateau tournant</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>Orbite</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>Vitesse de glissement</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>Roulis</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Vitesse de roulis</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>Construction du gamut…</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>pas de gamut</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>Afficher / masquer</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>Enveloppe de gamut 3D</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>Coupe de gamut 2D</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>Plan</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>Liaison</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>Créateur d’affichage V4</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>Affichage RVB V5</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>déposez un profil d’affichage</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>Observateur V5 (PCC)</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>déposez un profil d’observateur</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Créer le profil d’affichage V4</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>Nom du profil</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Créer</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>Création…</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>Annuler</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} fichier(s) non chargé(s)</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
+        <v>Pipeline de liaison</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>OK</v>
+        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Terminé</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>ou</v>
+        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>Choisir un fichier</v>
+        <v>Vérification de l'image…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>En-tête</v>
+        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>Balises</v>
+        <v>Transformer l'image</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>Validation</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>Analyse</v>
+        <v>Déposez des profils pour démarrer la chaîne</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>supprimé</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Déplacer plus tôt</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Déplacer plus tard</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>Déplacer vers le haut</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>Intention de rendu</v>
+        <v>Déplacer vers le bas</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% encre</v>
+        <v>Intention de rendu (tout)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>Perceptif</v>
+        <v>Intention de rendu pour cette transformation</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Les transformations utilisent des intentions de rendu différentes</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>Saturation</v>
+        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>Statistiques du profil</v>
+        <v>Chaîne</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>La chaîne n'a pas pu être analysée.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Vérification de la chaîne…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>Intention de rendu</v>
+        <v>La chaîne ne se connecte pas ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Corrigez la chaîne avant de traiter des images</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>moyenne</v>
+        <v>Créer un DeviceLink</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>Nom du DeviceLink</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>max</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>Analyse en cours…</v>
+        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>Analyse</v>
+        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Créez une chaîne pour traiter des images</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>Tracé</v>
+        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>Sortie brute</v>
+        <v>Image transformée enregistrée.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>Courbes</v>
+        <v>Fichier de données trop volumineux.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Transformer les données</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>Courbes de sortie</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>Image CLUT</v>
+        <v>Préférer</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>Image de gamut</v>
+        <v>Observateur</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>Chromaticité</v>
+        <v>Illuminant</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>Nuage de points</v>
+        <v>Condition</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Filtrer {n} doublon(s)</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>Table de la courbe</v>
+        <v>médiane</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>Tables</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Données</v>
+        <v>échantillons</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>Évaluer</v>
+        <v>{n} doublons</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>Chargement…</v>
+        <v>Résultat de la transformation</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>Entrée</v>
+        <v>{src} → {dst} · {n} échantillons</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>Sortie</v>
+        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>Virgule flottante</v>
+        <v>Enregistrer sous</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>Point de grille</v>
+        <v>Enregistrer</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>Normalisé</v>
+        <v>Inverser la transformation</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>Lisible</v>
+        <v>Inversion…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>Appareil → PCS</v>
+        <v>Inverser</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → Appareil</v>
+        <v>dernière étape</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>première étape</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>Chargement…</v>
+        <v>Données en {in} → recherche {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Coût ΔE</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Cette image contient un profil ICC intégré.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Extraire et ajouter à la chaîne</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Extraction…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Ignorer</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>Sécurité</v>
+        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>Conformité</v>
+        <v>Options de sortie de l'image</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>Qualité</v>
+        <v>Encodage</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>RAPPORT</v>
+        <v>Identique à la source</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>ÉCHEC</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>contrôles</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Flottant (32 bits)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Compression</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Aucune</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Planaire</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>S’abonner</v>
+        <v>Entrelacé</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Séparé</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Interpolation CMM</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>Fermer</v>
+        <v>Tétraédrique</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Linéaire</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>Adresse e-mail</v>
+        <v>Intégrer le profil ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>vous@exemple.com</v>
+        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Assembler un TIFF spectral</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(facultatif)</v>
+        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>can</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>Annuler</v>
+        <v>Assembler et enregistrer</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>S’abonner</v>
+        <v>Assemblage…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>{n} canaux assemblés.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>Fermer</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>Avis de confidentialité</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>Erreur :</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>Convertir en XML</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>Convertir en JSON</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>Convertir en ICC</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>Conversion en XML…</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>Charger un profil ICC</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>ID du profil</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>Nom de balise</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>Décalage</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>Taille</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>Rembourrage</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>Type</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>Tableau de {type}</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>octets</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>max</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>Le profil est valide</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>État de validation inconnu</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>Valide</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>Avertissement</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>Erreur</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>Inconnu</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>Réussi</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>Échec</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>Détail de validation</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>Déclenché par</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>Champ</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>Valeur actuelle</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>Requis : 0</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>Attendu : {value}</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>Non valide</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>Fermer</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>indentation</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>trier les clés</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Chargement du rapport Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Exécution des contrôles Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Rapport Profile Assessment WG</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Sécurité</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Conformité</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Qualité</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>RAPPORT</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>ÉCHEC</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>contrôles</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Outil de profil ICC</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Propulsé par {lib}</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>S’abonner</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Être notifié des nouvelles versions de profiletool</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Être notifié des nouvelles versions</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Adresse e-mail</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>vous@exemple.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Comment utiliserez-vous profiletool ?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(facultatif)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Annuler</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>S’abonner</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Merci — nous reviendrons vers vous.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Avis de confidentialité</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Veuillez saisir une adresse e-mail valide.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Erreur réseau. Veuillez réessayer.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Erreur :</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Convertir en XML</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Convertir en JSON</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Convertir en ICC</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Conversion en XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Conversion en JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Conversion en ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Charger un profil ICC</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>ID du profil</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Aucune balise trouvée.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Nom de balise</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Décalage</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Taille</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Rembourrage</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Octets modifiés depuis le chargement</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Type</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Tableau de {type}</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(Aucun contenu)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>octets</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Chargement de la description complète…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Impossible de charger la description complète :</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Le profil est valide</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Le profil comporte des avertissements</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Le profil est non conforme</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Erreur de validation critique</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1053,2669 +1053,2645 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>Téléversez un profil ICC pour le valider selon la spécification</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>à l’aide de l’implémentation de démonstration</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>.</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>Validation…</v>
+        <v>Profils</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Afficher le pool de profils</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>Réduire</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Profils</v>
+        <v>Charger des profils</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>Afficher le pool de profils</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>Réduire</v>
+        <v>Déposez des profils ICC ici</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>Charger des profils</v>
+        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>Retirer</v>
+        <v>Nouveau depuis .cube</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>Déposez des profils ICC ici</v>
+        <v>Trier par nom</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Nouveau depuis .cube</v>
+        <v>Nouveau profil depuis .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>Trier par nom</v>
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>Choisir un fichier .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>Nouveau profil depuis .cube</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Choisir un fichier .cube</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
         <v>ou déposez-le ici, ou collez ci-dessous</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Annuler</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Créer le DeviceLink</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Création…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>Annuler</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>Créer le DeviceLink</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>Création…</v>
+        <v>Comparer</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Lier</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>Profil</v>
+        <v>Spectral</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>Comparer</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>Lier</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>Spectral</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>Faites glisser des profils du pool vers cet onglet</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>Retirer</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>Aucun profil sélectionné</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>Rien à comparer pour l’instant</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>Comparaison de gamut</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>Intention de rendu</v>
+        <v>Numéros des axes</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>Enveloppe</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>Fil de fer</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>Numéros des axes</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>Opacité</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>Couleur</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>Uni</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>Par valeur</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>Par teinte</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>Rotation</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>Plateau tournant</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>Orbite</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>Vitesse de glissement</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>Roulis</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>Vitesse de roulis</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>Construction du gamut…</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>pas de gamut</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>Afficher / masquer</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>Enveloppe de gamut 3D</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>Coupe de gamut 2D</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>Plan</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>Liaison</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>Créateur d’affichage V4</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>Affichage RVB V5</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>déposez un profil d’affichage</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>Observateur V5 (PCC)</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>déposez un profil d’observateur</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>Créer le profil d’affichage V4</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>Nom du profil</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>Créer</v>
+        <v>Pipeline de liaison</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>Création…</v>
+        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
+        <v>Terminé</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>Pipeline de liaison</v>
+        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
+        <v>Vérification de l'image…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>Terminé</v>
+        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
+        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>Vérification de l'image…</v>
+        <v>Transformer l'image</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
+        <v>Déposez des profils pour démarrer la chaîne</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>Transformer l'image</v>
+        <v>supprimé</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>Transformation…</v>
+        <v>Déplacer plus tôt</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>Déposez des profils pour démarrer la chaîne</v>
+        <v>Déplacer plus tard</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>supprimé</v>
+        <v>Déplacer vers le haut</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>Déplacer plus tôt</v>
+        <v>Déplacer vers le bas</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>Déplacer plus tard</v>
+        <v>Intention de rendu (tout)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>Déplacer vers le haut</v>
+        <v>Intention de rendu pour cette transformation</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>Déplacer vers le bas</v>
+        <v>Les transformations utilisent des intentions de rendu différentes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>Intention de rendu (tout)</v>
+        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>Intention de rendu pour cette transformation</v>
+        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>Les transformations utilisent des intentions de rendu différentes</v>
+        <v>Chaîne</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
+        <v>La chaîne n'a pas pu être analysée.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
+        <v>Vérification de la chaîne…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>Chaîne</v>
+        <v>La chaîne ne se connecte pas ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>La chaîne n'a pas pu être analysée.</v>
+        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>Vérification de la chaîne…</v>
+        <v>Corrigez la chaîne avant de traiter des images</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>La chaîne ne se connecte pas ({detail}).</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
+        <v>Créer un DeviceLink</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>Corrigez la chaîne avant de traiter des images</v>
+        <v>Nom du DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>Effacer</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>Créer un DeviceLink</v>
+        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>Nom du DeviceLink</v>
+        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>Création…</v>
+        <v>Créez une chaîne pour traiter des images</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
+        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
+        <v>Image transformée enregistrée.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>Créez une chaîne pour traiter des images</v>
+        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>Image transformée enregistrée.</v>
+        <v>Fichier de données trop volumineux.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformer les données</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>Fichier de données trop volumineux.</v>
+        <v>Préférer</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>Transformer les données</v>
+        <v>Observateur</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>Transformation…</v>
+        <v>Illuminant</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>Préférer</v>
+        <v>Condition</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>Observateur</v>
+        <v>Filtrer {n} doublon(s)</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>Illuminant</v>
+        <v>médiane</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>Condition</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>Filtrer {n} doublon(s)</v>
+        <v>échantillons</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>médiane</v>
+        <v>{n} doublons</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>moyenne</v>
+        <v>Résultat de la transformation</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>échantillons</v>
+        <v>{src} → {dst} · {n} échantillons</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} doublons</v>
+        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>Résultat de la transformation</v>
+        <v>Enregistrer sous</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} échantillons</v>
+        <v>Enregistrer</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
+        <v>Inverser la transformation</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>Enregistrer sous</v>
+        <v>Inversion…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>Enregistrer</v>
+        <v>Inverser</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>Inverser la transformation</v>
+        <v>dernière étape</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>Inversion…</v>
+        <v>première étape</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverser</v>
+        <v>Données en {in} → recherche {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>dernière étape</v>
+        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>première étape</v>
+        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>Données en {in} → recherche {out}</v>
+        <v>Coût ΔE</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
+        <v>Cette image contient un profil ICC intégré.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
+        <v>Extraire et ajouter à la chaîne</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>Coût ΔE</v>
+        <v>Extraction…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>Cette image contient un profil ICC intégré.</v>
+        <v>Ignorer</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>Extraire et ajouter à la chaîne</v>
+        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>Extraction…</v>
+        <v>Options de sortie de l'image</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>Ignorer</v>
+        <v>Encodage</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
+        <v>Identique à la source</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>Options de sortie de l'image</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>Encodage</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>Identique à la source</v>
+        <v>Flottant (32 bits)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8 bits</v>
+        <v>Compression</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16 bits</v>
+        <v>Aucune</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>Flottant (32 bits)</v>
+        <v>Planaire</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>Compression</v>
+        <v>Entrelacé</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>Aucune</v>
+        <v>Séparé</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>Planaire</v>
+        <v>Interpolation CMM</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>Entrelacé</v>
+        <v>Tétraédrique</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>Séparé</v>
+        <v>Linéaire</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>Interpolation CMM</v>
+        <v>Intégrer le profil ICC</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>Tétraédrique</v>
+        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>Linéaire</v>
+        <v>Assembler un TIFF spectral</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>Intégrer le profil ICC</v>
+        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
+        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>Assembler un TIFF spectral</v>
+        <v>can</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
+        <v>Assembler et enregistrer</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
+        <v>Assemblage…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>can</v>
+        <v>{n} canaux assemblés.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>Assembler et enregistrer</v>
+        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>Assemblage…</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} canaux assemblés.</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>Annuler</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} fichier(s) non chargé(s)</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>OK</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>ou</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>Choisir un fichier</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>En-tête</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>Balises</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>Validation</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>Analyse</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>Intention de rendu</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% encre</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>Perceptif</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>Saturation</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>Statistiques du profil</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>Intention de rendu</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>ΔE aller-retour</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>max</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>moyenne</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>max</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>Analyse en cours…</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>Analyse</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>Tracé</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>Sortie brute</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>Courbes</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>Courbes de sortie</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>Image CLUT</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>Image de gamut</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>Chromaticité</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>Nuage de points</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>Table de la courbe</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>Tables</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>Données</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>Évaluer</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>Chargement…</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>Entrée</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>Sortie</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>Virgule flottante</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>Point de grille</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>Normalisé</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>Lisible</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>Appareil → PCS</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → Appareil</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>Chargement…</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>Sécurité</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>Conformité</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>Qualité</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>RAPPORT</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>ÉCHEC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>contrôles</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>S’abonner</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>Fermer</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>Adresse e-mail</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>vous@exemple.com</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(facultatif)</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>Annuler</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>S’abonner</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>Fermer</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>Erreur :</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>Convertir en XML</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>Convertir en JSON</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>Convertir en ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>Conversion en XML…</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>Conversion en ICC…</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>ID du profil</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>Nom de balise</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>Décalage</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>Taille</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>Rembourrage</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>Type</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>Tableau de {type}</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>octets</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>Le profil est valide</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>État de validation inconnu</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>Valide</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>Avertissement</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>Erreur</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>Inconnu</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>Réussi</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>Échec</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>Détail de validation</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>Déclenché par</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>Champ</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>Valeur actuelle</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>Requis : 0</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>Attendu : {value}</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>Non valide</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>Fermer</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>trier les clés</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>indentation</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>trier les clés</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B410"/>
+  <dimension ref="A1:B411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -413,3285 +413,3293 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>Aller-retour (PRMG)</v>
+        <v>{pct} % des échantillons étaient hors plage et ont été écrêtés.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>Aller-retour sur le cube périphérique du profil, identique à l’outil de référence iccRoundTrip. L’aller-retour 1 correspond à l’erreur périphérique→PCS→périphérique (ΔE*ab) ; l’aller-retour 2 mesure la stabilité de l’aller-retour PCS. L’histogramme PRMG indique l’interopérabilité par rapport au Perceptual Reference Medium Gamut.</v>
+        <v>Aller-retour (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>Utiliser les balises MPE (couleur)</v>
+        <v>Aller-retour sur le cube périphérique du profil, identique à l’outil de référence iccRoundTrip. L’aller-retour 1 correspond à l’erreur périphérique→PCS→périphérique (ΔE*ab) ; l’aller-retour 2 mesure la stabilité de l’aller-retour PCS. L’histogramme PRMG indique l’interopérabilité par rapport au Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>Ce profil ne peut pas faire d’aller-retour : il lui manque les transformations périphérique↔PCS requises (par ex. un profil unidirectionnel ou abstrait).</v>
+        <v>Utiliser les balises MPE (couleur)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>Aller-retour ignoré : l’espace colorimétrique du périphérique est trop large à évaluer (trop d’échantillons).</v>
+        <v>Ce profil ne peut pas faire d’aller-retour : il lui manque les transformations périphérique↔PCS requises (par ex. un profil unidirectionnel ou abstrait).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>Métrique</v>
+        <v>Aller-retour ignoré : l’espace colorimétrique du périphérique est trop large à évaluer (trop d’échantillons).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>Aller-retour 1</v>
+        <v>Métrique</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>Aller-retour 2</v>
+        <v>Aller-retour 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>périphérique → PCS → périphérique</v>
+        <v>Aller-retour 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>stabilité de l’aller-retour PCS</v>
+        <v>périphérique → PCS → périphérique</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>ΔE min</v>
+        <v>stabilité de l’aller-retour PCS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>ΔE moyen</v>
+        <v>ΔE min</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>ΔE max</v>
+        <v>ΔE moyen</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>Pire L, a, b</v>
+        <v>ΔE max</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>Gamut spécifié</v>
+        <v>Pire L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Gamut spécifié</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>Non spécifié</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>Non évalué</v>
+        <v>Non spécifié</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>Interopérabilité PRMG</v>
+        <v>Non évalué</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Interopérabilité PRMG</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>Nombre</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>Part</v>
+        <v>Nombre</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>Total</v>
+        <v>Part</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG non évalué</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>Mesures globales du profil pour une intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et une mesure de précision d’aller-retour. Choisissez l’intention de rendu et le type d’aller-retour — le tableau et l’histogramme se mettent à jour en conséquence.</v>
+        <v>PRMG non évalué</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>Type d’aller-retour</v>
+        <v>Mesures globales du profil pour une intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et une mesure de précision d’aller-retour. Choisissez l’intention de rendu et le type d’aller-retour — le tableau et l’histogramme se mettent à jour en conséquence.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Sans effet sur ce type d’aller-retour</v>
+        <v>Type d’aller-retour</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>Ce type d’aller-retour n’est pas disponible pour ce profil.</v>
+        <v>Sans effet sur ce type d’aller-retour</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>Distribution du ΔE d’aller-retour</v>
+        <v>Ce type d’aller-retour n’est pas disponible pour ce profil.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>Aucun échantillon d’aller-retour n’est tombé dans la région évaluée.</v>
+        <v>Distribution du ΔE d’aller-retour</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>Écart-type</v>
+        <v>Aucun échantillon d’aller-retour n’est tombé dans la région évaluée.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>Fréquence relative</v>
+        <v>Écart-type</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Fréquence cumulée</v>
+        <v>Fréquence relative</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>Échelle horizontale</v>
+        <v>Fréquence cumulée</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>ΔE entier</v>
+        <v>Échelle horizontale</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>Échelle automatique</v>
+        <v>ΔE entier</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>Classes</v>
+        <v>Échelle automatique</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>Image CLUT</v>
+        <v>Classes</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>La table de correspondance des couleurs (CLUT) d’une transformation périphérique↔PCS, disposée en mosaïque dans une image. Choisissez la table d’intention de rendu à afficher.</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>Ce profil n’a pas de tables périphérique↔PCS basées sur une CLUT à visualiser.</v>
+        <v>La table de correspondance des couleurs (CLUT) d’une transformation périphérique↔PCS, disposée en mosaïque dans une image. Choisissez la table d’intention de rendu à afficher.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>Image de gamut</v>
+        <v>Ce profil n’a pas de tables périphérique↔PCS basées sur une CLUT à visualiser.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>La carte intérieur/extérieur du gamut de la balise gamut : neutre là où une couleur PCS est reproductible, rouge là où elle sort du gamut du périphérique.</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>Ce profil n’a pas de balise gamut à visualiser.</v>
+        <v>La carte intérieur/extérieur du gamut de la balise gamut : neutre là où une couleur PCS est reproductible, rouge là où elle sort du gamut du périphérique.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>Échelle verticale</v>
+        <v>Ce profil n’a pas de balise gamut à visualiser.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>Échelle verticale</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>Augmentation tonale</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>Augmentation tonale (sortie − entrée)</v>
+        <v>Augmentation tonale</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>Afficher le vidage complet</v>
+        <v>Augmentation tonale (sortie − entrée)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>Sortie tronquée pour des raisons de performance.</v>
+        <v>Afficher le vidage complet</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>Aperçu dans le gamut (RT0)</v>
+        <v>Sortie tronquée pour des raisons de performance.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Aperçu dans le gamut (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>Reproductibilité (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>Interopérabilité PRMG</v>
+        <v>Reproductibilité (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>Aperçu iccviz : une grille de valeurs périphérique est convertie en PCS, de nouveau en périphérique, puis à nouveau en PCS ; le ΔE*ab est mesuré entre les deux passages PCS. Un contrôle rapide de stabilité dans le gamut.</v>
+        <v>Interopérabilité PRMG</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip Aller-retour 1 : ΔE*ab entre le PCS de chaque couleur périphérique et son PCS après un aller-retour Lab → périphérique → Lab. Reflète la précision d’inversion et le mappage de gamut.</v>
+        <v>Aperçu iccviz : une grille de valeurs périphérique est convertie en PCS, de nouveau en périphérique, puis à nouveau en PCS ; le ΔE*ab est mesuré entre les deux passages PCS. Un contrôle rapide de stabilité dans le gamut.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Aller-retour 2 : ΔE*ab entre le premier et le second aller-retour — la stabilité d’un aller-retour PCS répété (reproductibilité, indépendamment de l’écrêtage de gamut du premier trajet).</v>
+        <v>iccRoundTrip Aller-retour 1 : ΔE*ab entre le PCS de chaque couleur périphérique et son PCS après un aller-retour Lab → périphérique → Lab. Reflète la précision d’inversion et le mappage de gamut.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG : les couleurs PCS à l’intérieur du Perceptual Reference Medium Gamut font un aller-retour unique (Lab → périphérique → Lab) ; la distribution du ΔE*ab indique l’interopérabilité inter-profils.</v>
+        <v>iccRoundTrip Aller-retour 2 : ΔE*ab entre le premier et le second aller-retour — la stabilité d’un aller-retour PCS répété (reproductibilité, indépendamment de l’écrêtage de gamut du premier trajet).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>Paramètres</v>
+        <v>iccRoundTrip PRMG : les couleurs PCS à l’intérieur du Perceptual Reference Medium Gamut font un aller-retour unique (Lab → périphérique → Lab) ; la distribution du ΔE*ab indique l’interopérabilité inter-profils.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>Affichage</v>
+        <v>Paramètres</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>Arrière-plan</v>
+        <v>Affichage</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>Langue</v>
+        <v>Arrière-plan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>Système</v>
+        <v>Langue</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>Clair</v>
+        <v>Système</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>Sombre</v>
+        <v>Clair</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>Par défaut du système</v>
+        <v>Sombre</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>Format des nombres</v>
+        <v>Par défaut du système</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>Hexadécimal</v>
+        <v>Format des nombres</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>Décimal</v>
+        <v>Hexadécimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>Aide</v>
+        <v>Décimal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>Contact</v>
+        <v>Aide</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>Guide de l’utilisateur</v>
+        <v>Contact</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>Rechercher dans le guide</v>
+        <v>Guide de l’utilisateur</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>Rechercher dans le guide de l’utilisateur</v>
+        <v>Rechercher dans le guide</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>Résultat précédent</v>
+        <v>Rechercher dans le guide de l’utilisateur</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>Résultat suivant</v>
+        <v>Résultat précédent</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>Fermer le guide</v>
+        <v>Résultat suivant</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Chargement…</v>
+        <v>Fermer le guide</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Impossible de charger le guide de l’utilisateur.</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>Aucun</v>
+        <v>Impossible de charger le guide de l’utilisateur.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Aucun</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>Validation…</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>Profils</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>Afficher le pool de profils</v>
+        <v>Profils</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>Réduire</v>
+        <v>Afficher le pool de profils</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>Charger des profils</v>
+        <v>Réduire</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>Retirer</v>
+        <v>Charger des profils</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>Déposez des profils ICC ici</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
+        <v>Déposez des profils ICC ici</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>Nouveau depuis .cube</v>
+        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>Trier par nom</v>
+        <v>Nouveau depuis .cube</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>Trier par nom</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>Nouveau profil depuis .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
+        <v>Nouveau profil depuis .cube</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>Choisir un fichier .cube</v>
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Choisir un fichier .cube</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>ou déposez-le ici, ou collez ci-dessous</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Annuler</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>Créer le DeviceLink</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>Création…</v>
+        <v>Créer le DeviceLink</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>Profil</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>Comparer</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>Lier</v>
+        <v>Comparer</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>Spectral</v>
+        <v>Lier</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>Faites glisser des profils du pool vers cet onglet</v>
+        <v>Spectral</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>Retirer</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>Aucun profil sélectionné</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>Rien à comparer pour l’instant</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>Comparaison de gamut</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>Intention de rendu</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>Enveloppe</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>Fil de fer</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>Numéros des axes</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>Opacité</v>
+        <v>Numéros des axes</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Couleur</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Uni</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Par valeur</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Par teinte</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Rotation</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Plateau tournant</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Orbite</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Vitesse de glissement</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Roulis</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Vitesse de roulis</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Construction du gamut…</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>pas de gamut</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>Afficher / masquer</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Enveloppe de gamut 3D</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Coupe de gamut 2D</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Plan</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Liaison</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Créateur d’affichage V4</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>Affichage RVB V5</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>déposez un profil d’affichage</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>Observateur V5 (PCC)</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>déposez un profil d’observateur</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Créer le profil d’affichage V4</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Nom du profil</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Créer</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Création…</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Pipeline de liaison</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
+        <v>Pipeline de liaison</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>Terminé</v>
+        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
+        <v>Terminé</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>Vérification de l'image…</v>
+        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
+        <v>Vérification de l'image…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
+        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>Transformer l'image</v>
+        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformation…</v>
+        <v>Transformer l'image</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>Déposez des profils pour démarrer la chaîne</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>supprimé</v>
+        <v>Déposez des profils pour démarrer la chaîne</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>Déplacer plus tôt</v>
+        <v>supprimé</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>Déplacer plus tard</v>
+        <v>Déplacer plus tôt</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>Déplacer vers le haut</v>
+        <v>Déplacer plus tard</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>Déplacer vers le bas</v>
+        <v>Déplacer vers le haut</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>Intention de rendu (tout)</v>
+        <v>Déplacer vers le bas</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>Intention de rendu pour cette transformation</v>
+        <v>Intention de rendu (tout)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>Les transformations utilisent des intentions de rendu différentes</v>
+        <v>Intention de rendu pour cette transformation</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
+        <v>Les transformations utilisent des intentions de rendu différentes</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
+        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>Chaîne</v>
+        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>La chaîne n'a pas pu être analysée.</v>
+        <v>Chaîne</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>Vérification de la chaîne…</v>
+        <v>La chaîne n'a pas pu être analysée.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>La chaîne ne se connecte pas ({detail}).</v>
+        <v>Vérification de la chaîne…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
+        <v>La chaîne ne se connecte pas ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>Corrigez la chaîne avant de traiter des images</v>
+        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>Effacer</v>
+        <v>Corrigez la chaîne avant de traiter des images</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>Créer un DeviceLink</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>Nom du DeviceLink</v>
+        <v>Créer un DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>Création…</v>
+        <v>Nom du DeviceLink</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
+        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>Créez une chaîne pour traiter des images</v>
+        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
+        <v>Créez une chaîne pour traiter des images</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>Image transformée enregistrée.</v>
+        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
+        <v>Image transformée enregistrée.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>Fichier de données trop volumineux.</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>Transformer les données</v>
+        <v>Fichier de données trop volumineux.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformation…</v>
+        <v>Transformer les données</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>Préférer</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>Observateur</v>
+        <v>Préférer</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>Illuminant</v>
+        <v>Observateur</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>Filtrer {n} doublon(s)</v>
+        <v>Condition</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>médiane</v>
+        <v>Filtrer {n} doublon(s)</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>moyenne</v>
+        <v>médiane</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>échantillons</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} doublons</v>
+        <v>échantillons</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>Résultat de la transformation</v>
+        <v>{n} doublons</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} échantillons</v>
+        <v>Résultat de la transformation</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
+        <v>{src} → {dst} · {n} échantillons</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>Enregistrer sous</v>
+        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>Enregistrer</v>
+        <v>Enregistrer sous</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>Inverser la transformation</v>
+        <v>Enregistrer</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>Inversion…</v>
+        <v>Inverser la transformation</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>Inverser</v>
+        <v>Inversion…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>dernière étape</v>
+        <v>Inverser</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>première étape</v>
+        <v>dernière étape</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>Données en {in} → recherche {out}</v>
+        <v>première étape</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
+        <v>Données en {in} → recherche {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
+        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>Coût ΔE</v>
+        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>Cette image contient un profil ICC intégré.</v>
+        <v>Coût ΔE</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Extraire et ajouter à la chaîne</v>
+        <v>Cette image contient un profil ICC intégré.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extraction…</v>
+        <v>Extraire et ajouter à la chaîne</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>Ignorer</v>
+        <v>Extraction…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
+        <v>Ignorer</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>Options de sortie de l'image</v>
+        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>Encodage</v>
+        <v>Options de sortie de l'image</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>Identique à la source</v>
+        <v>Encodage</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8 bits</v>
+        <v>Identique à la source</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>Flottant (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>Compression</v>
+        <v>Flottant (32 bits)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>Aucune</v>
+        <v>Compression</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>Planaire</v>
+        <v>Aucune</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>Entrelacé</v>
+        <v>Planaire</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>Séparé</v>
+        <v>Entrelacé</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>Interpolation CMM</v>
+        <v>Séparé</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>Tétraédrique</v>
+        <v>Interpolation CMM</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>Linéaire</v>
+        <v>Tétraédrique</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>Intégrer le profil ICC</v>
+        <v>Linéaire</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
+        <v>Intégrer le profil ICC</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>Assembler un TIFF spectral</v>
+        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
+        <v>Assembler un TIFF spectral</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
+        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>can</v>
+        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>Assembler et enregistrer</v>
+        <v>can</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>Assemblage…</v>
+        <v>Assembler et enregistrer</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>{n} canaux assemblés.</v>
+        <v>Assemblage…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
+        <v>{n} canaux assemblés.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>Annuler</v>
+        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} fichier(s) non chargé(s)</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>OK</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>ou</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>Choisir un fichier</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>En-tête</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>Balises</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>Validation</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>Analyse</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>Intention de rendu</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% encre</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>Perceptif</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>Saturation</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>Statistiques du profil</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>Intention de rendu</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>moyenne</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>Analyse en cours…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>Analyse</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>Tracé</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>Sortie brute</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>Courbes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>Courbes de sortie</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Image CLUT</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>Image de gamut</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>Chromaticité</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>Nuage de points</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>Table de la courbe</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>Tables</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>Données</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>Évaluer</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>Chargement…</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>Entrée</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>Sortie</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>Virgule flottante</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>Point de grille</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>Normalisé</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>Lisible</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>Appareil → PCS</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → Appareil</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>Chargement…</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>Sécurité</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>Conformité</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>Qualité</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>RAPPORT</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2555,1151 +2555,1423 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>Perceptif</v>
+        <v>L* en sortie (tonalité)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>Saturation</v>
+        <v>Colorimétrie des extrêmes</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>Statistiques du profil</v>
+        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Relative</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Absolue</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>Intention de rendu</v>
+        <v>Point blanc</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Point noir</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Encrage au point noir</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>moyenne</v>
+        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>max</v>
+        <v>Aplat et chroma maximal</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>Analyse en cours…</v>
+        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>Analyse</v>
+        <v>Teinte</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Aplat</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>Tracé</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>Sortie brute</v>
+        <v>À l’encrage</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>Utilisation d’encre dans les ombres</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>Courbes</v>
+        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>Courbes d’entrée</v>
+        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>Courbes de sortie</v>
+        <v>Plan à L* constante</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>Image CLUT</v>
+        <v>avec compensation du point noir depuis</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>Image de gamut</v>
+        <v>Position le long du trajet</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>Chromaticité</v>
+        <v>Trajet</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>Nuage de points</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>Table de la courbe</v>
+        <v>Jaune</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>Tables</v>
+        <v>Rouge</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>Données</v>
+        <v>Vert</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>Évaluer</v>
+        <v>Bleu</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>Chargement…</v>
+        <v>Noir</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>Entrée</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>Sortie</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>Virgule flottante</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>Point de grille</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>Normalisé</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>Lisible</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>Appareil → PCS</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → Appareil</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>Chargement…</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>URL de profil non valide :</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>max</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>Sécurité</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>Conformité</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>Qualité</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>RAPPORT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>ÉCHEC</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>contrôles</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>S’abonner</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>Fermer</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>Adresse e-mail</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>vous@exemple.com</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(facultatif)</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>Annuler</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>S’abonner</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>Fermer</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>Erreur :</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>Convertir en XML</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>Convertir en JSON</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>Convertir en ICC</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>Conversion en XML…</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>Conversion en JSON…</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>Conversion en ICC…</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>Charger un profil ICC</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>ID du profil</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>Nom de balise</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>Décalage</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>Taille</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>Rembourrage</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>Type</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>Tableau de {type}</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>octets</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>Le profil est valide</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>État de validation inconnu</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>Valide</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>Avertissement</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>Erreur</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>Inconnu</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>Réussi</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>Échec</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>Détail de validation</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>Déclenché par</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>Champ</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>Valeur actuelle</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>Requis : 0</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>Attendu : {value}</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>Non valide</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>Fermer</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>indentation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>trier les clés</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>Le profil est valide</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>Le profil comporte des avertissements</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>Le profil est non conforme</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Erreur de validation critique</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -533,3445 +533,3477 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>Gamut spécifié</v>
+        <v>ΔE d’aller-retour par clarté</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (clarté de la couleur demandée)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>Non spécifié</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>Non évalué</v>
+        <v>points, limite du gamut → neutre</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>Interopérabilité PRMG</v>
+        <v>Gamut spécifié</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>Nombre</v>
+        <v>Non spécifié</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>Part</v>
+        <v>Non évalué</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>Total</v>
+        <v>Interopérabilité PRMG</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG non évalué</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>Mesures globales du profil pour une intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et une mesure de précision d’aller-retour. Choisissez l’intention de rendu et le type d’aller-retour — le tableau et l’histogramme se mettent à jour en conséquence.</v>
+        <v>Nombre</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>Type d’aller-retour</v>
+        <v>Part</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>Sans effet sur ce type d’aller-retour</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>Ce type d’aller-retour n’est pas disponible pour ce profil.</v>
+        <v>PRMG non évalué</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>Distribution du ΔE d’aller-retour</v>
+        <v>Mesures globales du profil pour une intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et une mesure de précision d’aller-retour. Choisissez l’intention de rendu et le type d’aller-retour — le tableau et l’histogramme se mettent à jour en conséquence.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>Aucun échantillon d’aller-retour n’est tombé dans la région évaluée.</v>
+        <v>Type d’aller-retour</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>Écart-type</v>
+        <v>Sans effet sur ce type d’aller-retour</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>Fréquence relative</v>
+        <v>Ce type d’aller-retour n’est pas disponible pour ce profil.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>Fréquence cumulée</v>
+        <v>Distribution du ΔE d’aller-retour</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>Échelle horizontale</v>
+        <v>Aucun échantillon d’aller-retour n’est tombé dans la région évaluée.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>ΔE entier</v>
+        <v>Écart-type</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>Échelle automatique</v>
+        <v>Fréquence relative</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>Classes</v>
+        <v>Fréquence cumulée</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>Image CLUT</v>
+        <v>Échelle horizontale</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>La table de correspondance des couleurs (CLUT) d’une transformation périphérique↔PCS, disposée en mosaïque dans une image. Choisissez la table d’intention de rendu à afficher.</v>
+        <v>ΔE entier</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>Ce profil n’a pas de tables périphérique↔PCS basées sur une CLUT à visualiser.</v>
+        <v>Échelle automatique</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>Image de gamut</v>
+        <v>Classes</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>La carte intérieur/extérieur du gamut de la balise gamut : neutre là où une couleur PCS est reproductible, rouge là où elle sort du gamut du périphérique.</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>Ce profil n’a pas de balise gamut à visualiser.</v>
+        <v>La table de correspondance des couleurs (CLUT) d’une transformation périphérique↔PCS, disposée en mosaïque dans une image. Choisissez la table d’intention de rendu à afficher.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>Échelle verticale</v>
+        <v>Ce profil n’a pas de tables périphérique↔PCS basées sur une CLUT à visualiser.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>Augmentation tonale</v>
+        <v>La carte intérieur/extérieur du gamut de la balise gamut : neutre là où une couleur PCS est reproductible, rouge là où elle sort du gamut du périphérique.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>Augmentation tonale (sortie − entrée)</v>
+        <v>Ce profil n’a pas de balise gamut à visualiser.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>Afficher le vidage complet</v>
+        <v>Échelle verticale</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>Sortie tronquée pour des raisons de performance.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>Aperçu dans le gamut (RT0)</v>
+        <v>Augmentation tonale</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Augmentation tonale (sortie − entrée)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>Reproductibilité (RT2)</v>
+        <v>Afficher le vidage complet</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>Interopérabilité PRMG</v>
+        <v>Sortie tronquée pour des raisons de performance.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>Aperçu iccviz : une grille de valeurs périphérique est convertie en PCS, de nouveau en périphérique, puis à nouveau en PCS ; le ΔE*ab est mesuré entre les deux passages PCS. Un contrôle rapide de stabilité dans le gamut.</v>
+        <v>Aperçu dans le gamut (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Aller-retour 1 : ΔE*ab entre le PCS de chaque couleur périphérique et son PCS après un aller-retour Lab → périphérique → Lab. Reflète la précision d’inversion et le mappage de gamut.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip Aller-retour 2 : ΔE*ab entre le premier et le second aller-retour — la stabilité d’un aller-retour PCS répété (reproductibilité, indépendamment de l’écrêtage de gamut du premier trajet).</v>
+        <v>Reproductibilité (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG : les couleurs PCS à l’intérieur du Perceptual Reference Medium Gamut font un aller-retour unique (Lab → périphérique → Lab) ; la distribution du ΔE*ab indique l’interopérabilité inter-profils.</v>
+        <v>Interopérabilité PRMG</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>Paramètres</v>
+        <v>Aperçu iccviz : une grille de valeurs périphérique est convertie en PCS, de nouveau en périphérique, puis à nouveau en PCS ; le ΔE*ab est mesuré entre les deux passages PCS. Un contrôle rapide de stabilité dans le gamut.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>Affichage</v>
+        <v>iccRoundTrip Aller-retour 1 : ΔE*ab entre le PCS de chaque couleur périphérique et son PCS après un aller-retour Lab → périphérique → Lab. Reflète la précision d’inversion et le mappage de gamut.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>Arrière-plan</v>
+        <v>iccRoundTrip Aller-retour 2 : ΔE*ab entre le premier et le second aller-retour — la stabilité d’un aller-retour PCS répété (reproductibilité, indépendamment de l’écrêtage de gamut du premier trajet).</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>Langue</v>
+        <v>iccRoundTrip PRMG : les couleurs PCS à l’intérieur du Perceptual Reference Medium Gamut font un aller-retour unique (Lab → périphérique → Lab) ; la distribution du ΔE*ab indique l’interopérabilité inter-profils.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>Système</v>
+        <v>Paramètres</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>Clair</v>
+        <v>Affichage</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>Sombre</v>
+        <v>Arrière-plan</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>Par défaut du système</v>
+        <v>Langue</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>Format des nombres</v>
+        <v>Système</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>Hexadécimal</v>
+        <v>Clair</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>Décimal</v>
+        <v>Sombre</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>Aide</v>
+        <v>Par défaut du système</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>Contact</v>
+        <v>Format des nombres</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>Guide de l’utilisateur</v>
+        <v>Hexadécimal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>Rechercher dans le guide</v>
+        <v>Décimal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>Rechercher dans le guide de l’utilisateur</v>
+        <v>Aide</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>Résultat précédent</v>
+        <v>Contact</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>Résultat suivant</v>
+        <v>Guide de l’utilisateur</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Fermer le guide</v>
+        <v>Rechercher dans le guide</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>Chargement…</v>
+        <v>Rechercher dans le guide de l’utilisateur</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>Impossible de charger le guide de l’utilisateur.</v>
+        <v>Résultat précédent</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>Aucun</v>
+        <v>Résultat suivant</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Fermer le guide</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>Basé sur l’implémentation de démonstration</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Impossible de charger le guide de l’utilisateur.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>Validation…</v>
+        <v>Aucun</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>Enregistrer le profil ICC</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● Modifié — non enregistré</v>
+        <v>Basé sur l’implémentation de démonstration</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>Profils</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>Afficher le pool de profils</v>
+        <v>Validation…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>Réduire</v>
+        <v>Enregistrer le profil ICC</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>Charger des profils</v>
+        <v>● Modifié — non enregistré</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>Retirer</v>
+        <v>Profils</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>Déposez des profils ICC ici</v>
+        <v>Afficher le pool de profils</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
+        <v>Réduire</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>Nouveau depuis .cube</v>
+        <v>Charger des profils</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>Trier par nom</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>Déposez des profils ICC ici</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>Nouveau profil depuis .cube</v>
+        <v>ou une image (TIFF/PNG/JPEG) pour en extraire le profil intégré — les fichiers restent sur votre appareil.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
+        <v>Nouveau depuis .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>Choisir un fichier .cube</v>
+        <v>Trier par nom</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Nouveau profil depuis .cube</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Choisir un fichier .cube</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>ou déposez-le ici, ou collez ci-dessous</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Annuler</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Créer le DeviceLink</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Création…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Impossible de lire ce fichier.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>Profil</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>Comparer</v>
+        <v>Créer le DeviceLink</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>Lier</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>Spectral</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>Faites glisser des profils du pool vers cet onglet</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>Retirer</v>
+        <v>Comparer</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>Aucun profil sélectionné</v>
+        <v>Lier</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
+        <v>Spectral</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>Rien à comparer pour l’instant</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>Comparaison de gamut</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>Intention de rendu</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>Enveloppe</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>Fil de fer</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>Numéros des axes</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacité</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>Couleur</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>Uni</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>Par valeur</v>
+        <v>Numéros des axes</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>Par teinte</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotation</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>Plateau tournant</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>Orbite</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>Vitesse de glissement</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>Roulis</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>Vitesse de roulis</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>Construction du gamut…</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>pas de gamut</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>Afficher / masquer</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>Enveloppe de gamut 3D</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>Coupe de gamut 2D</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>Plan</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>Liaison</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>Créateur d’affichage V4</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>Affichage RVB V5</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>déposez un profil d’affichage</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>Observateur V5 (PCC)</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>déposez un profil d’observateur</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Créer le profil d’affichage V4</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>Nom du profil</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Créer</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>Création…</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>Pipeline de liaison</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>Terminé</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>Vérification de l'image…</v>
+        <v>Pipeline de liaison</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
+        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
+        <v>Terminé</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformer l'image</v>
+        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>Transformation…</v>
+        <v>Vérification de l'image…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>Déposez des profils pour démarrer la chaîne</v>
+        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>supprimé</v>
+        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>Déplacer plus tôt</v>
+        <v>Transformer l'image</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>Déplacer plus tard</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>Déplacer vers le haut</v>
+        <v>Déposez des profils pour démarrer la chaîne</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>Déplacer vers le bas</v>
+        <v>supprimé</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>Intention de rendu (tout)</v>
+        <v>Déplacer plus tôt</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>Intention de rendu pour cette transformation</v>
+        <v>Déplacer plus tard</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>Les transformations utilisent des intentions de rendu différentes</v>
+        <v>Déplacer vers le haut</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
+        <v>Déplacer vers le bas</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
+        <v>Intention de rendu (tout)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>Chaîne</v>
+        <v>Intention de rendu pour cette transformation</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>La chaîne n'a pas pu être analysée.</v>
+        <v>Les transformations utilisent des intentions de rendu différentes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>Vérification de la chaîne…</v>
+        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>La chaîne ne se connecte pas ({detail}).</v>
+        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
+        <v>Chaîne</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>Corrigez la chaîne avant de traiter des images</v>
+        <v>La chaîne n'a pas pu être analysée.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>Effacer</v>
+        <v>Vérification de la chaîne…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>Créer un DeviceLink</v>
+        <v>La chaîne ne se connecte pas ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Nom du DeviceLink</v>
+        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>Création…</v>
+        <v>Corrigez la chaîne avant de traiter des images</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
+        <v>Créer un DeviceLink</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>Créez une chaîne pour traiter des images</v>
+        <v>Nom du DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>Image transformée enregistrée.</v>
+        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
+        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Créez une chaîne pour traiter des images</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>Fichier de données trop volumineux.</v>
+        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformer les données</v>
+        <v>Image transformée enregistrée.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>Transformation…</v>
+        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>Préférer</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>Observateur</v>
+        <v>Fichier de données trop volumineux.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>Illuminant</v>
+        <v>Transformer les données</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>Condition</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>Filtrer {n} doublon(s)</v>
+        <v>Préférer</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>médiane</v>
+        <v>Observateur</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>moyenne</v>
+        <v>Illuminant</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>échantillons</v>
+        <v>Condition</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} doublons</v>
+        <v>Filtrer {n} doublon(s)</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>Résultat de la transformation</v>
+        <v>médiane</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} échantillons</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
+        <v>échantillons</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>Enregistrer sous</v>
+        <v>{n} doublons</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>Enregistrer</v>
+        <v>Résultat de la transformation</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>Inverser la transformation</v>
+        <v>{src} → {dst} · {n} échantillons</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>Inversion…</v>
+        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>Inverser</v>
+        <v>Enregistrer sous</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>dernière étape</v>
+        <v>Enregistrer</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>première étape</v>
+        <v>Inverser la transformation</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>Données en {in} → recherche {out}</v>
+        <v>Inversion…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
+        <v>Inverser</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
+        <v>dernière étape</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>Coût ΔE</v>
+        <v>première étape</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>Cette image contient un profil ICC intégré.</v>
+        <v>Données en {in} → recherche {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extraire et ajouter à la chaîne</v>
+        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>Extraction…</v>
+        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>Ignorer</v>
+        <v>Coût ΔE</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
+        <v>Cette image contient un profil ICC intégré.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>Options de sortie de l'image</v>
+        <v>Extraire et ajouter à la chaîne</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>Encodage</v>
+        <v>Extraction…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>Identique à la source</v>
+        <v>Ignorer</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8 bits</v>
+        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16 bits</v>
+        <v>Options de sortie de l'image</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>Flottant (32 bits)</v>
+        <v>Encodage</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>Compression</v>
+        <v>Identique à la source</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>Aucune</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>Planaire</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>Entrelacé</v>
+        <v>Flottant (32 bits)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>Séparé</v>
+        <v>Compression</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>Interpolation CMM</v>
+        <v>Aucune</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>Tétraédrique</v>
+        <v>Planaire</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>Linéaire</v>
+        <v>Entrelacé</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>Intégrer le profil ICC</v>
+        <v>Séparé</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
+        <v>Interpolation CMM</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>Assembler un TIFF spectral</v>
+        <v>Tétraédrique</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
+        <v>Linéaire</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
+        <v>Intégrer le profil ICC</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>can</v>
+        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>Assembler et enregistrer</v>
+        <v>Assembler un TIFF spectral</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>Assemblage…</v>
+        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>{n} canaux assemblés.</v>
+        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
+        <v>can</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>Annuler</v>
+        <v>Assembler et enregistrer</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} fichier(s) non chargé(s)</v>
+        <v>Assemblage…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
+        <v>{n} canaux assemblés.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>OK</v>
+        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>ou</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>Choisir un fichier</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>En-tête</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>Balises</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>Validation</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>Analyse</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>Intention de rendu</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% encre</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* en sortie (tonalité)</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimétrie des extrêmes</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
+        <v>L* en sortie (tonalité)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>Absolue</v>
+        <v>Colorimétrie des extrêmes</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>Point blanc</v>
+        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>Point noir</v>
+        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>Encrage au point noir</v>
+        <v>Relative</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>Absolue</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
+        <v>Point blanc</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
+        <v>Point noir</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Aplat et chroma maximal</v>
+        <v>Encrage au point noir</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>Teinte</v>
+        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>Aplat</v>
+        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>C* max</v>
+        <v>Aplat et chroma maximal</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>À l’encrage</v>
+        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
+        <v>Teinte</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>Utilisation d’encre dans les ombres</v>
+        <v>Aplat</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>À l’encrage</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>Plan à L* constante</v>
+        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>avec compensation du point noir depuis</v>
+        <v>Utilisation d’encre dans les ombres</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>Position le long du trajet</v>
+        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>Trajet</v>
+        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>Cyan</v>
+        <v>Plan à L* constante</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>Magenta</v>
+        <v>avec compensation du point noir depuis</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>Jaune</v>
+        <v>Position le long du trajet</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>Rouge</v>
+        <v>Trajet</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>Vert</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>Bleu</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>Noir</v>
+        <v>Jaune</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>Perceptif</v>
+        <v>Rouge</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Vert</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>Saturation</v>
+        <v>Bleu</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Noir</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>Statistiques du profil</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>Intention de rendu</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>moyenne</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>max</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>Analyse en cours…</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>Analyse</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>Tracé</v>
+        <v>max</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>Sortie brute</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>Courbes</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>Courbes de sortie</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>Image CLUT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>Image de gamut</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>Chromaticité</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>Nuage de points</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>Table de la courbe</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>Tables</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>Données</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>Évaluer</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>Chargement…</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>Entrée</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>Sortie</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>Virgule flottante</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>Point de grille</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>Normalisé</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Lisible</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>Appareil → PCS</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → Appareil</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>Chargement…</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>URL de profil non valide :</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>Sécurité</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>Conformité</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>Qualité</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>RAPPORT</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>ÉCHEC</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>contrôles</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>Outil de profil ICC</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>S’abonner</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>Fermer</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>Adresse e-mail</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>vous@exemple.com</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(facultatif)</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>Annuler</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>S’abonner</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>Fermer</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>Avis de confidentialité</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>Erreur :</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>Convertir en XML</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>Convertir en JSON</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>Convertir en ICC</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>Conversion en XML…</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>ID du profil</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>Nom de balise</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>Décalage</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>Taille</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>Rembourrage</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>Type</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>Tableau de {type}</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>octets</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>Le profil est valide</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>État de validation inconnu</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>Valide</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>Avertissement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>Erreur</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>Inconnu</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>Réussi</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>Échec</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>Détail de validation</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>Déclenché par</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>Champ</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>Valeur actuelle</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>Requis : 0</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>Attendu : {value}</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>Non valide</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>Fermer</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>indentation</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>trier les clés</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -2803,1207 +2803,1343 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>Cyan</v>
+        <v>Chemins d’encrage primaire par le neutre</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>Magenta</v>
+        <v>Trois chemins dans le gamut — cyan→rouge, magenta→vert, jaune→bleu — chacun passant par l’axe neutre à la clarté médiane de ses extrémités, à travers la table B2A sélectionnée. Chaque échantillon est dans le gamut, donc contrairement aux chemins d’ombre, toute rupture ou inversion d’un colorant traduit un défaut de régularité de la CLUT plutôt qu’un artefact de mappage de gamut.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>Jaune</v>
+        <v>Les chemins d’encrage primaire ne sont disponibles que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>Rouge</v>
+        <v>Position le long du chemin (neutre au milieu)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>Vert</v>
+        <v>Compensation du point noir appliquée pour cette intention.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>Bleu</v>
+        <v>Statistiques d’utilisation d’encre</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>Noir</v>
+        <v>La quantité de chaque colorant déposée par le profil, en somme et en part du total — la signature de consommation d’encre de la séparation.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>Perceptif</v>
+        <v>Les statistiques d’utilisation d’encre ne sont disponibles que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Axe neutre</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>Saturation</v>
+        <v>Couverture moyenne</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Part d’encre</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>Statistiques du profil</v>
+        <v>La part d’encre est l’empreinte de la construction du neutre — la fraction de chaque colorant dans le total d’encre déposée, indépendamment du nombre d’échantillons.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Points dans le gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>L’utilisation d’encre sur toutes les couleurs du gamut nécessite la frontière de gamut côté B2A, pas encore implémentée — à venir.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>Intention de rendu</v>
+        <v>Aucune donnée de colorant à résumer.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Sélectionnez une table B2A (PCS→périphérique) ci-dessous pour afficher aussi une image de couverture d’encre en niveaux de gris pour chaque colorant.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Couverture d’encre de chaque colorant sur la même grille (plus sombre = plus d’encre).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>moyenne</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>Jaune</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>max</v>
+        <v>Rouge</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>Analyse en cours…</v>
+        <v>Vert</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>Analyse</v>
+        <v>Bleu</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Noir</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>Tracé</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>Sortie brute</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>Courbes</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>Courbes de sortie</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>Image CLUT</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>Image de gamut</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>Chromaticité</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>Nuage de points</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>Table de la courbe</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>Données</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>Évaluer</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>Chargement…</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>Entrée</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Sortie</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>Virgule flottante</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>Point de grille</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>Normalisé</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Lisible</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Appareil → PCS</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → Appareil</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>Chargement…</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>Sécurité</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>Conformité</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>Qualité</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>RAPPORT</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>ÉCHEC</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>contrôles</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>S’abonner</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>Fermer</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>Adresse e-mail</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>vous@exemple.com</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(facultatif)</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>Annuler</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>S’abonner</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>Fermer</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>Erreur :</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>Convertir en XML</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>Convertir en JSON</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>Convertir en ICC</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>Conversion en XML…</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>Conversion en JSON…</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>Charger un profil ICC</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>ID du profil</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>Nom de balise</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>Décalage</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>Taille</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Rembourrage</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>Type</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>Tableau de {type}</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>octets</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>Le profil est valide</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>Erreur de validation critique</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>État de validation inconnu</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>Valide</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>Avertissement</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>Erreur</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>Inconnu</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>Réussi</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>Échec</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>Détail de validation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>Déclenché par</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>Champ</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>Valeur actuelle</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>Requis : 0</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>Attendu : {value}</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>Non valide</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>Fermer</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>indentation</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>trier les clés</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
   </ignoredErrors>
 </worksheet>
 </file>